--- a/experiment/SRForm2_bestx4/Test/results-B100/B100.xlsx
+++ b/experiment/SRForm2_bestx4/Test/results-B100/B100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.95</v>
+        <v>23.97</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5664</v>
+        <v>0.5687</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28.58</v>
+        <v>28.6</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8095</v>
+        <v>0.8106</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.32</v>
+        <v>26.43</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8098</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.57</v>
+        <v>30.6</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8467</v>
+        <v>0.8469</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.19</v>
+        <v>26.21</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7060999999999999</v>
+        <v>0.7075</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.76</v>
+        <v>33.89</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8919</v>
+        <v>0.8928</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26.13</v>
+        <v>26.14</v>
       </c>
       <c r="C8" t="n">
-        <v>0.741</v>
+        <v>0.7431</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23.01</v>
+        <v>22.99</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5863</v>
+        <v>0.5891999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27.38</v>
+        <v>27.37</v>
       </c>
       <c r="C10" t="n">
         <v>0.7838000000000001</v>
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29.22</v>
+        <v>29.24</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8001</v>
+        <v>0.8013</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24.19</v>
+        <v>24.33</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7135</v>
+        <v>0.7242</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>27.8</v>
+        <v>27.88</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7422</v>
+        <v>0.7461</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29.92</v>
+        <v>29.95</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8053</v>
+        <v>0.8064</v>
       </c>
     </row>
     <row r="15">
@@ -624,7 +624,7 @@
         <v>29.23</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8254</v>
+        <v>0.8268</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24.96</v>
+        <v>24.98</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6742</v>
+        <v>0.6764</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24.48</v>
+        <v>24.47</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7482</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>34.52</v>
+        <v>34.6</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8905999999999999</v>
+        <v>0.8913</v>
       </c>
     </row>
     <row r="19">
@@ -676,7 +676,7 @@
         <v>32.8</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8905999999999999</v>
+        <v>0.8912</v>
       </c>
     </row>
     <row r="20">
@@ -689,7 +689,7 @@
         <v>26.12</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7337</v>
+        <v>0.7339</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25.85</v>
+        <v>25.92</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7941</v>
+        <v>0.7967</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22</v>
+        <v>22.09</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6762</v>
+        <v>0.6837</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23.66</v>
+        <v>23.69</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6166</v>
+        <v>0.6219</v>
       </c>
     </row>
     <row r="24">
@@ -741,7 +741,7 @@
         <v>24.79</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5695</v>
+        <v>0.5709</v>
       </c>
     </row>
     <row r="25">
@@ -754,7 +754,7 @@
         <v>26.44</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7859</v>
+        <v>0.7864</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>27.51</v>
+        <v>27.42</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8169</v>
+        <v>0.8159</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26.82</v>
+        <v>26.71</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8332000000000001</v>
+        <v>0.8336</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27.62</v>
+        <v>27.66</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.7326</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29.48</v>
+        <v>29.5</v>
       </c>
       <c r="C29" t="n">
-        <v>0.7975</v>
+        <v>0.7996</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.19</v>
+        <v>32.24</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8968</v>
+        <v>0.8973</v>
       </c>
     </row>
     <row r="31">
@@ -832,7 +832,7 @@
         <v>19.84</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5</v>
+        <v>0.5016</v>
       </c>
     </row>
     <row r="32">
@@ -845,7 +845,7 @@
         <v>29.68</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8149</v>
+        <v>0.8146</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>20.89</v>
+        <v>20.87</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4246</v>
+        <v>0.4289</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25.1</v>
+        <v>25.11</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6661</v>
+        <v>0.6698</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>24.29</v>
+        <v>24.33</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7519</v>
+        <v>0.7533</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>34.58</v>
+        <v>34.75</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8892</v>
+        <v>0.8911</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26.88</v>
+        <v>26.87</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7382</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>27.89</v>
+        <v>27.92</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5124</v>
+        <v>0.5129</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28.11</v>
+        <v>28.16</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7126</v>
+        <v>0.7147</v>
       </c>
     </row>
     <row r="40">
@@ -949,7 +949,7 @@
         <v>28.39</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7393</v>
+        <v>0.741</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>35.3</v>
+        <v>35.46</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9507</v>
+        <v>0.9517</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26.77</v>
+        <v>26.79</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.7408</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25.69</v>
+        <v>25.75</v>
       </c>
       <c r="C43" t="n">
-        <v>0.715</v>
+        <v>0.7185</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26.57</v>
+        <v>26.6</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7552</v>
+        <v>0.7564</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>27.75</v>
+        <v>27.76</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8706</v>
+        <v>0.8708</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24.53</v>
+        <v>24.58</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.6687</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>34.56</v>
+        <v>34.59</v>
       </c>
       <c r="C47" t="n">
-        <v>0.869</v>
+        <v>0.8692</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>22.61</v>
+        <v>22.57</v>
       </c>
       <c r="C48" t="n">
-        <v>0.615</v>
+        <v>0.6152</v>
       </c>
     </row>
     <row r="49">
@@ -1066,7 +1066,7 @@
         <v>24.9</v>
       </c>
       <c r="C49" t="n">
-        <v>0.6291</v>
+        <v>0.6306</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>26.84</v>
+        <v>26.89</v>
       </c>
       <c r="C50" t="n">
-        <v>0.8652</v>
+        <v>0.8678</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>32.12</v>
+        <v>32.1</v>
       </c>
       <c r="C51" t="n">
-        <v>0.8387</v>
+        <v>0.8386</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>24.7</v>
+        <v>24.72</v>
       </c>
       <c r="C52" t="n">
-        <v>0.6122</v>
+        <v>0.6136</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>22.39</v>
+        <v>22.41</v>
       </c>
       <c r="C53" t="n">
-        <v>0.7006</v>
+        <v>0.7024</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>32.35</v>
+        <v>32.47</v>
       </c>
       <c r="C54" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.8439</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>32.53</v>
+        <v>32.49</v>
       </c>
       <c r="C55" t="n">
-        <v>0.7988</v>
+        <v>0.7978</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>27.55</v>
+        <v>27.59</v>
       </c>
       <c r="C56" t="n">
-        <v>0.7696</v>
+        <v>0.7729</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25.45</v>
+        <v>25.51</v>
       </c>
       <c r="C57" t="n">
-        <v>0.6872</v>
+        <v>0.6899</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>21.39</v>
+        <v>21.41</v>
       </c>
       <c r="C58" t="n">
-        <v>0.4178</v>
+        <v>0.4202</v>
       </c>
     </row>
     <row r="59">
@@ -1196,7 +1196,7 @@
         <v>27.4</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7231</v>
+        <v>0.7237</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>31.97</v>
+        <v>31.98</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7906</v>
+        <v>0.791</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>31.17</v>
+        <v>31.23</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7833</v>
+        <v>0.7842</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.66</v>
+        <v>31.73</v>
       </c>
       <c r="C62" t="n">
-        <v>0.8124</v>
+        <v>0.8141</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>28.81</v>
+        <v>28.87</v>
       </c>
       <c r="C63" t="n">
-        <v>0.7899</v>
+        <v>0.7903</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>33.32</v>
+        <v>33.51</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9507</v>
+        <v>0.9514</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>24.2</v>
+        <v>24.22</v>
       </c>
       <c r="C65" t="n">
-        <v>0.6655</v>
+        <v>0.6673</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>25.92</v>
+        <v>25.91</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6163999999999999</v>
+        <v>0.6176</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>28.14</v>
+        <v>28.24</v>
       </c>
       <c r="C67" t="n">
-        <v>0.7874</v>
+        <v>0.7912</v>
       </c>
     </row>
     <row r="68">
@@ -1310,7 +1310,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>39.44</v>
+        <v>39.55</v>
       </c>
       <c r="C68" t="n">
         <v>0.98</v>
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>20.88</v>
+        <v>20.82</v>
       </c>
       <c r="C69" t="n">
-        <v>0.5692</v>
+        <v>0.571</v>
       </c>
     </row>
     <row r="70">
@@ -1339,7 +1339,7 @@
         <v>22.71</v>
       </c>
       <c r="C70" t="n">
-        <v>0.6456</v>
+        <v>0.6468</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>28.62</v>
+        <v>28.64</v>
       </c>
       <c r="C71" t="n">
-        <v>0.802</v>
+        <v>0.8023</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>30.19</v>
+        <v>30.31</v>
       </c>
       <c r="C72" t="n">
-        <v>0.8106</v>
+        <v>0.8139</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>25.42</v>
+        <v>25.44</v>
       </c>
       <c r="C73" t="n">
-        <v>0.5931999999999999</v>
+        <v>0.5946</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>27.18</v>
+        <v>27.17</v>
       </c>
       <c r="C74" t="n">
-        <v>0.6029</v>
+        <v>0.6025</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>26.23</v>
+        <v>26.24</v>
       </c>
       <c r="C75" t="n">
-        <v>0.6944</v>
+        <v>0.6949</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>23.91</v>
+        <v>24.03</v>
       </c>
       <c r="C76" t="n">
-        <v>0.6879</v>
+        <v>0.6919999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>30.63</v>
+        <v>30.6</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7837</v>
+        <v>0.7831</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>23.64</v>
+        <v>23.61</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4769</v>
+        <v>0.4773</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>29.79</v>
+        <v>29.8</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8093</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>32.14</v>
+        <v>32.31</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9486</v>
+        <v>0.9493</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>29.75</v>
+        <v>29.76</v>
       </c>
       <c r="C81" t="n">
-        <v>0.8181</v>
+        <v>0.8191000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>35.66</v>
+        <v>35.68</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9372</v>
+        <v>0.9377</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>28.45</v>
+        <v>28.48</v>
       </c>
       <c r="C83" t="n">
-        <v>0.7151</v>
+        <v>0.7165</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22.16</v>
+        <v>22.15</v>
       </c>
       <c r="C84" t="n">
-        <v>0.5229</v>
+        <v>0.5263</v>
       </c>
     </row>
     <row r="85">
@@ -1534,7 +1534,7 @@
         <v>21.01</v>
       </c>
       <c r="C85" t="n">
-        <v>0.5992</v>
+        <v>0.6045</v>
       </c>
     </row>
     <row r="86">
@@ -1547,7 +1547,7 @@
         <v>25.47</v>
       </c>
       <c r="C86" t="n">
-        <v>0.7819</v>
+        <v>0.7827</v>
       </c>
     </row>
     <row r="87">
@@ -1560,7 +1560,7 @@
         <v>24.91</v>
       </c>
       <c r="C87" t="n">
-        <v>0.5921</v>
+        <v>0.5951</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27.3</v>
+        <v>27.33</v>
       </c>
       <c r="C88" t="n">
-        <v>0.6901</v>
+        <v>0.6923</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>30.53</v>
+        <v>30.57</v>
       </c>
       <c r="C89" t="n">
-        <v>0.8092</v>
+        <v>0.8107</v>
       </c>
     </row>
     <row r="90">
@@ -1599,7 +1599,7 @@
         <v>27.22</v>
       </c>
       <c r="C90" t="n">
-        <v>0.5595</v>
+        <v>0.5604</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>24.97</v>
+        <v>24.98</v>
       </c>
       <c r="C91" t="n">
-        <v>0.637</v>
+        <v>0.6394</v>
       </c>
     </row>
     <row r="92">
@@ -1625,7 +1625,7 @@
         <v>29.01</v>
       </c>
       <c r="C92" t="n">
-        <v>0.7092000000000001</v>
+        <v>0.7106</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>26.33</v>
+        <v>26.45</v>
       </c>
       <c r="C93" t="n">
-        <v>0.7412</v>
+        <v>0.7458</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>30.59</v>
+        <v>30.82</v>
       </c>
       <c r="C94" t="n">
-        <v>0.8754</v>
+        <v>0.8769</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>25.7</v>
+        <v>25.74</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7053</v>
+        <v>0.7069</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>25.88</v>
+        <v>25.95</v>
       </c>
       <c r="C96" t="n">
-        <v>0.7905</v>
+        <v>0.7937</v>
       </c>
     </row>
     <row r="97">
@@ -1690,7 +1690,7 @@
         <v>21.91</v>
       </c>
       <c r="C97" t="n">
-        <v>0.3155</v>
+        <v>0.3158</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>26.97</v>
+        <v>26.98</v>
       </c>
       <c r="C98" t="n">
-        <v>0.5577</v>
+        <v>0.5592</v>
       </c>
     </row>
     <row r="99">
@@ -1716,7 +1716,7 @@
         <v>26.12</v>
       </c>
       <c r="C99" t="n">
-        <v>0.7739</v>
+        <v>0.7743</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>26.78</v>
+        <v>26.81</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7297</v>
+        <v>0.7321</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>24.89</v>
+        <v>24.92</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7179</v>
+        <v>0.7208</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>27.4</v>
+        <v>27.43</v>
       </c>
       <c r="C102" t="n">
-        <v>0.7307</v>
+        <v>0.7324000000000001</v>
       </c>
     </row>
   </sheetData>
